--- a/services/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
+++ b/services/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,1103 +413,1118 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HK46"/>
+  <dimension ref="A1:HN46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>freq</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>siec</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>geo\TIME_PERIOD</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2008-01</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>2008-02</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>2008-03</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>2008-04</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>2008-05</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>2008-06</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>2008-07</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>2008-08</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>2008-09</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>2008-10</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>2008-11</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>2008-12</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>2009-01</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>2009-02</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>2009-03</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>2009-04</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>2009-05</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>2009-06</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>2009-07</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>2009-08</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>2009-09</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>2009-10</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>2009-11</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>2009-12</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>2010-01</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>2010-02</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>2010-03</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>2010-04</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>2010-05</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>2010-06</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>2010-07</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>2010-08</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>2010-09</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>2010-10</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>2010-11</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>2010-12</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>2011-01</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>2011-02</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>2011-03</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>2011-04</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>2011-05</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>2011-06</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>2011-07</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>2011-08</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>2011-09</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>2011-10</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>2011-11</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>2011-12</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>2012-01</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>2012-02</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>2012-03</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>2012-04</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>2012-05</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>2012-06</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>2012-07</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>2012-08</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>2012-09</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>2012-10</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>2012-11</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>2012-12</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>2013-01</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>2013-02</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>2013-03</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>2013-04</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>2013-05</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>2013-06</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>2013-07</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>2013-08</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>2013-09</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>2013-10</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BX1" t="inlineStr">
         <is>
           <t>2013-11</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BY1" t="inlineStr">
         <is>
           <t>2013-12</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="BZ1" t="inlineStr">
         <is>
           <t>2014-01</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CA1" t="inlineStr">
         <is>
           <t>2014-02</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CB1" t="inlineStr">
         <is>
           <t>2014-03</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CC1" t="inlineStr">
         <is>
           <t>2014-04</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CD1" t="inlineStr">
         <is>
           <t>2014-05</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CE1" t="inlineStr">
         <is>
           <t>2014-06</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CF1" t="inlineStr">
         <is>
           <t>2014-07</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CG1" t="inlineStr">
         <is>
           <t>2014-08</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CH1" t="inlineStr">
         <is>
           <t>2014-09</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CI1" t="inlineStr">
         <is>
           <t>2014-10</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CJ1" t="inlineStr">
         <is>
           <t>2014-11</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CK1" t="inlineStr">
         <is>
           <t>2014-12</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CL1" t="inlineStr">
         <is>
           <t>2015-01</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CM1" t="inlineStr">
         <is>
           <t>2015-02</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CN1" t="inlineStr">
         <is>
           <t>2015-03</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CO1" t="inlineStr">
         <is>
           <t>2015-04</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CP1" t="inlineStr">
         <is>
           <t>2015-05</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CQ1" t="inlineStr">
         <is>
           <t>2015-06</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CR1" t="inlineStr">
         <is>
           <t>2015-07</t>
         </is>
       </c>
-      <c r="CS1" s="1" t="inlineStr">
+      <c r="CS1" t="inlineStr">
         <is>
           <t>2015-08</t>
         </is>
       </c>
-      <c r="CT1" s="1" t="inlineStr">
+      <c r="CT1" t="inlineStr">
         <is>
           <t>2015-09</t>
         </is>
       </c>
-      <c r="CU1" s="1" t="inlineStr">
+      <c r="CU1" t="inlineStr">
         <is>
           <t>2015-10</t>
         </is>
       </c>
-      <c r="CV1" s="1" t="inlineStr">
+      <c r="CV1" t="inlineStr">
         <is>
           <t>2015-11</t>
         </is>
       </c>
-      <c r="CW1" s="1" t="inlineStr">
+      <c r="CW1" t="inlineStr">
         <is>
           <t>2015-12</t>
         </is>
       </c>
-      <c r="CX1" s="1" t="inlineStr">
+      <c r="CX1" t="inlineStr">
         <is>
           <t>2016-01</t>
         </is>
       </c>
-      <c r="CY1" s="1" t="inlineStr">
+      <c r="CY1" t="inlineStr">
         <is>
           <t>2016-02</t>
         </is>
       </c>
-      <c r="CZ1" s="1" t="inlineStr">
+      <c r="CZ1" t="inlineStr">
         <is>
           <t>2016-03</t>
         </is>
       </c>
-      <c r="DA1" s="1" t="inlineStr">
+      <c r="DA1" t="inlineStr">
         <is>
           <t>2016-04</t>
         </is>
       </c>
-      <c r="DB1" s="1" t="inlineStr">
+      <c r="DB1" t="inlineStr">
         <is>
           <t>2016-05</t>
         </is>
       </c>
-      <c r="DC1" s="1" t="inlineStr">
+      <c r="DC1" t="inlineStr">
         <is>
           <t>2016-06</t>
         </is>
       </c>
-      <c r="DD1" s="1" t="inlineStr">
+      <c r="DD1" t="inlineStr">
         <is>
           <t>2016-07</t>
         </is>
       </c>
-      <c r="DE1" s="1" t="inlineStr">
+      <c r="DE1" t="inlineStr">
         <is>
           <t>2016-08</t>
         </is>
       </c>
-      <c r="DF1" s="1" t="inlineStr">
+      <c r="DF1" t="inlineStr">
         <is>
           <t>2016-09</t>
         </is>
       </c>
-      <c r="DG1" s="1" t="inlineStr">
+      <c r="DG1" t="inlineStr">
         <is>
           <t>2016-10</t>
         </is>
       </c>
-      <c r="DH1" s="1" t="inlineStr">
+      <c r="DH1" t="inlineStr">
         <is>
           <t>2016-11</t>
         </is>
       </c>
-      <c r="DI1" s="1" t="inlineStr">
+      <c r="DI1" t="inlineStr">
         <is>
           <t>2016-12</t>
         </is>
       </c>
-      <c r="DJ1" s="1" t="inlineStr">
+      <c r="DJ1" t="inlineStr">
         <is>
           <t>2017-01</t>
         </is>
       </c>
-      <c r="DK1" s="1" t="inlineStr">
+      <c r="DK1" t="inlineStr">
         <is>
           <t>2017-02</t>
         </is>
       </c>
-      <c r="DL1" s="1" t="inlineStr">
+      <c r="DL1" t="inlineStr">
         <is>
           <t>2017-03</t>
         </is>
       </c>
-      <c r="DM1" s="1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>2017-04</t>
         </is>
       </c>
-      <c r="DN1" s="1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>2017-05</t>
         </is>
       </c>
-      <c r="DO1" s="1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>2017-06</t>
         </is>
       </c>
-      <c r="DP1" s="1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>2017-07</t>
         </is>
       </c>
-      <c r="DQ1" s="1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>2017-08</t>
         </is>
       </c>
-      <c r="DR1" s="1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>2017-09</t>
         </is>
       </c>
-      <c r="DS1" s="1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>2017-10</t>
         </is>
       </c>
-      <c r="DT1" s="1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>2017-11</t>
         </is>
       </c>
-      <c r="DU1" s="1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>2017-12</t>
         </is>
       </c>
-      <c r="DV1" s="1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>2018-01</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>2018-02</t>
         </is>
       </c>
-      <c r="DX1" s="1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>2018-03</t>
         </is>
       </c>
-      <c r="DY1" s="1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>2018-04</t>
         </is>
       </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>2018-05</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>2018-06</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>2018-07</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>2018-08</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>2018-09</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>2018-10</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>2018-11</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>2018-12</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>2019-01</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>2019-02</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>2019-03</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>2019-04</t>
         </is>
       </c>
-      <c r="EL1" s="1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>2019-05</t>
         </is>
       </c>
-      <c r="EM1" s="1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
         <is>
           <t>2019-06</t>
         </is>
       </c>
-      <c r="EN1" s="1" t="inlineStr">
+      <c r="EN1" t="inlineStr">
         <is>
           <t>2019-07</t>
         </is>
       </c>
-      <c r="EO1" s="1" t="inlineStr">
+      <c r="EO1" t="inlineStr">
         <is>
           <t>2019-08</t>
         </is>
       </c>
-      <c r="EP1" s="1" t="inlineStr">
+      <c r="EP1" t="inlineStr">
         <is>
           <t>2019-09</t>
         </is>
       </c>
-      <c r="EQ1" s="1" t="inlineStr">
+      <c r="EQ1" t="inlineStr">
         <is>
           <t>2019-10</t>
         </is>
       </c>
-      <c r="ER1" s="1" t="inlineStr">
+      <c r="ER1" t="inlineStr">
         <is>
           <t>2019-11</t>
         </is>
       </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>2019-12</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="ET1" t="inlineStr">
         <is>
           <t>2020-01</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
+      <c r="EU1" t="inlineStr">
         <is>
           <t>2020-02</t>
         </is>
       </c>
-      <c r="EV1" s="1" t="inlineStr">
+      <c r="EV1" t="inlineStr">
         <is>
           <t>2020-03</t>
         </is>
       </c>
-      <c r="EW1" s="1" t="inlineStr">
+      <c r="EW1" t="inlineStr">
         <is>
           <t>2020-04</t>
         </is>
       </c>
-      <c r="EX1" s="1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>2020-05</t>
         </is>
       </c>
-      <c r="EY1" s="1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
         <is>
           <t>2020-06</t>
         </is>
       </c>
-      <c r="EZ1" s="1" t="inlineStr">
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>2020-07</t>
         </is>
       </c>
-      <c r="FA1" s="1" t="inlineStr">
+      <c r="FA1" t="inlineStr">
         <is>
           <t>2020-08</t>
         </is>
       </c>
-      <c r="FB1" s="1" t="inlineStr">
+      <c r="FB1" t="inlineStr">
         <is>
           <t>2020-09</t>
         </is>
       </c>
-      <c r="FC1" s="1" t="inlineStr">
+      <c r="FC1" t="inlineStr">
         <is>
           <t>2020-10</t>
         </is>
       </c>
-      <c r="FD1" s="1" t="inlineStr">
+      <c r="FD1" t="inlineStr">
         <is>
           <t>2020-11</t>
         </is>
       </c>
-      <c r="FE1" s="1" t="inlineStr">
+      <c r="FE1" t="inlineStr">
         <is>
           <t>2020-12</t>
         </is>
       </c>
-      <c r="FF1" s="1" t="inlineStr">
+      <c r="FF1" t="inlineStr">
         <is>
           <t>2021-01</t>
         </is>
       </c>
-      <c r="FG1" s="1" t="inlineStr">
+      <c r="FG1" t="inlineStr">
         <is>
           <t>2021-02</t>
         </is>
       </c>
-      <c r="FH1" s="1" t="inlineStr">
+      <c r="FH1" t="inlineStr">
         <is>
           <t>2021-03</t>
         </is>
       </c>
-      <c r="FI1" s="1" t="inlineStr">
+      <c r="FI1" t="inlineStr">
         <is>
           <t>2021-04</t>
         </is>
       </c>
-      <c r="FJ1" s="1" t="inlineStr">
+      <c r="FJ1" t="inlineStr">
         <is>
           <t>2021-05</t>
         </is>
       </c>
-      <c r="FK1" s="1" t="inlineStr">
+      <c r="FK1" t="inlineStr">
         <is>
           <t>2021-06</t>
         </is>
       </c>
-      <c r="FL1" s="1" t="inlineStr">
+      <c r="FL1" t="inlineStr">
         <is>
           <t>2021-07</t>
         </is>
       </c>
-      <c r="FM1" s="1" t="inlineStr">
+      <c r="FM1" t="inlineStr">
         <is>
           <t>2021-08</t>
         </is>
       </c>
-      <c r="FN1" s="1" t="inlineStr">
+      <c r="FN1" t="inlineStr">
         <is>
           <t>2021-09</t>
         </is>
       </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FO1" t="inlineStr">
         <is>
           <t>2021-10</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FP1" t="inlineStr">
         <is>
           <t>2021-11</t>
         </is>
       </c>
-      <c r="FQ1" s="1" t="inlineStr">
+      <c r="FQ1" t="inlineStr">
         <is>
           <t>2021-12</t>
         </is>
       </c>
-      <c r="FR1" s="1" t="inlineStr">
+      <c r="FR1" t="inlineStr">
         <is>
           <t>2022-01</t>
         </is>
       </c>
-      <c r="FS1" s="1" t="inlineStr">
+      <c r="FS1" t="inlineStr">
         <is>
           <t>2022-02</t>
         </is>
       </c>
-      <c r="FT1" s="1" t="inlineStr">
+      <c r="FT1" t="inlineStr">
         <is>
           <t>2022-03</t>
         </is>
       </c>
-      <c r="FU1" s="1" t="inlineStr">
+      <c r="FU1" t="inlineStr">
         <is>
           <t>2022-04</t>
         </is>
       </c>
-      <c r="FV1" s="1" t="inlineStr">
+      <c r="FV1" t="inlineStr">
         <is>
           <t>2022-05</t>
         </is>
       </c>
-      <c r="FW1" s="1" t="inlineStr">
+      <c r="FW1" t="inlineStr">
         <is>
           <t>2022-06</t>
         </is>
       </c>
-      <c r="FX1" s="1" t="inlineStr">
+      <c r="FX1" t="inlineStr">
         <is>
           <t>2022-07</t>
         </is>
       </c>
-      <c r="FY1" s="1" t="inlineStr">
+      <c r="FY1" t="inlineStr">
         <is>
           <t>2022-08</t>
         </is>
       </c>
-      <c r="FZ1" s="1" t="inlineStr">
+      <c r="FZ1" t="inlineStr">
         <is>
           <t>2022-09</t>
         </is>
       </c>
-      <c r="GA1" s="1" t="inlineStr">
+      <c r="GA1" t="inlineStr">
         <is>
           <t>2022-10</t>
         </is>
       </c>
-      <c r="GB1" s="1" t="inlineStr">
+      <c r="GB1" t="inlineStr">
         <is>
           <t>2022-11</t>
         </is>
       </c>
-      <c r="GC1" s="1" t="inlineStr">
+      <c r="GC1" t="inlineStr">
         <is>
           <t>2022-12</t>
         </is>
       </c>
-      <c r="GD1" s="1" t="inlineStr">
+      <c r="GD1" t="inlineStr">
         <is>
           <t>2023-01</t>
         </is>
       </c>
-      <c r="GE1" s="1" t="inlineStr">
+      <c r="GE1" t="inlineStr">
         <is>
           <t>2023-02</t>
         </is>
       </c>
-      <c r="GF1" s="1" t="inlineStr">
+      <c r="GF1" t="inlineStr">
         <is>
           <t>2023-03</t>
         </is>
       </c>
-      <c r="GG1" s="1" t="inlineStr">
+      <c r="GG1" t="inlineStr">
         <is>
           <t>2023-04</t>
         </is>
       </c>
-      <c r="GH1" s="1" t="inlineStr">
+      <c r="GH1" t="inlineStr">
         <is>
           <t>2023-05</t>
         </is>
       </c>
-      <c r="GI1" s="1" t="inlineStr">
+      <c r="GI1" t="inlineStr">
         <is>
           <t>2023-06</t>
         </is>
       </c>
-      <c r="GJ1" s="1" t="inlineStr">
+      <c r="GJ1" t="inlineStr">
         <is>
           <t>2023-07</t>
         </is>
       </c>
-      <c r="GK1" s="1" t="inlineStr">
+      <c r="GK1" t="inlineStr">
         <is>
           <t>2023-08</t>
         </is>
       </c>
-      <c r="GL1" s="1" t="inlineStr">
+      <c r="GL1" t="inlineStr">
         <is>
           <t>2023-09</t>
         </is>
       </c>
-      <c r="GM1" s="1" t="inlineStr">
+      <c r="GM1" t="inlineStr">
         <is>
           <t>2023-10</t>
         </is>
       </c>
-      <c r="GN1" s="1" t="inlineStr">
+      <c r="GN1" t="inlineStr">
         <is>
           <t>2023-11</t>
         </is>
       </c>
-      <c r="GO1" s="1" t="inlineStr">
+      <c r="GO1" t="inlineStr">
         <is>
           <t>2023-12</t>
         </is>
       </c>
-      <c r="GP1" s="1" t="inlineStr">
+      <c r="GP1" t="inlineStr">
         <is>
           <t>2024-01</t>
         </is>
       </c>
-      <c r="GQ1" s="1" t="inlineStr">
+      <c r="GQ1" t="inlineStr">
         <is>
           <t>2024-02</t>
         </is>
       </c>
-      <c r="GR1" s="1" t="inlineStr">
+      <c r="GR1" t="inlineStr">
         <is>
           <t>2024-03</t>
         </is>
       </c>
-      <c r="GS1" s="1" t="inlineStr">
+      <c r="GS1" t="inlineStr">
         <is>
           <t>2024-04</t>
         </is>
       </c>
-      <c r="GT1" s="1" t="inlineStr">
+      <c r="GT1" t="inlineStr">
         <is>
           <t>2024-05</t>
         </is>
       </c>
-      <c r="GU1" s="1" t="inlineStr">
+      <c r="GU1" t="inlineStr">
         <is>
           <t>2024-06</t>
         </is>
       </c>
-      <c r="GV1" s="1" t="inlineStr">
+      <c r="GV1" t="inlineStr">
         <is>
           <t>2024-07</t>
         </is>
       </c>
-      <c r="GW1" s="1" t="inlineStr">
+      <c r="GW1" t="inlineStr">
         <is>
           <t>2024-08</t>
         </is>
       </c>
-      <c r="GX1" s="1" t="inlineStr">
+      <c r="GX1" t="inlineStr">
         <is>
           <t>2024-09</t>
         </is>
       </c>
-      <c r="GY1" s="1" t="inlineStr">
+      <c r="GY1" t="inlineStr">
         <is>
           <t>2024-10</t>
         </is>
       </c>
-      <c r="GZ1" s="1" t="inlineStr">
+      <c r="GZ1" t="inlineStr">
         <is>
           <t>2024-11</t>
         </is>
       </c>
-      <c r="HA1" s="1" t="inlineStr">
+      <c r="HA1" t="inlineStr">
         <is>
           <t>2024-12</t>
         </is>
       </c>
-      <c r="HB1" s="1" t="inlineStr">
+      <c r="HB1" t="inlineStr">
         <is>
           <t>2025-01</t>
         </is>
       </c>
-      <c r="HC1" s="1" t="inlineStr">
+      <c r="HC1" t="inlineStr">
         <is>
           <t>2025-02</t>
         </is>
       </c>
-      <c r="HD1" s="1" t="inlineStr">
+      <c r="HD1" t="inlineStr">
         <is>
           <t>2025-03</t>
         </is>
       </c>
-      <c r="HE1" s="1" t="inlineStr">
+      <c r="HE1" t="inlineStr">
         <is>
           <t>2025-04</t>
         </is>
       </c>
-      <c r="HF1" s="1" t="inlineStr">
+      <c r="HF1" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="HG1" s="1" t="inlineStr">
+      <c r="HG1" t="inlineStr">
         <is>
           <t>2025-06</t>
         </is>
       </c>
-      <c r="HH1" s="1" t="inlineStr">
+      <c r="HH1" t="inlineStr">
         <is>
           <t>2025-07</t>
         </is>
       </c>
-      <c r="HI1" s="1" t="inlineStr">
+      <c r="HI1" t="inlineStr">
         <is>
           <t>2025-08</t>
         </is>
       </c>
-      <c r="HJ1" s="1" t="inlineStr">
+      <c r="HJ1" t="inlineStr">
         <is>
           <t>2025-09</t>
         </is>
       </c>
-      <c r="HK1" s="1" t="inlineStr">
+      <c r="HK1" t="inlineStr">
         <is>
           <t>2025-10</t>
+        </is>
+      </c>
+      <c r="HL1" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="HM1" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="HN1" t="inlineStr">
+        <is>
+          <t>2026-01</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -2186,9 +2189,18 @@
       <c r="HK2" t="n">
         <v>5947.434</v>
       </c>
+      <c r="HL2" t="n">
+        <v>5477.14</v>
+      </c>
+      <c r="HM2" t="n">
+        <v>5376.178</v>
+      </c>
+      <c r="HN2" t="n">
+        <v>6054.729</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -2853,9 +2865,18 @@
       <c r="HK3" t="n">
         <v>1522.94</v>
       </c>
+      <c r="HL3" t="n">
+        <v>1725.164</v>
+      </c>
+      <c r="HM3" t="n">
+        <v>2160.013</v>
+      </c>
+      <c r="HN3" t="n">
+        <v>2609.748</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -3328,9 +3349,18 @@
       <c r="HK4" t="n">
         <v>25.607</v>
       </c>
+      <c r="HL4" t="n">
+        <v>31.498</v>
+      </c>
+      <c r="HM4" t="n">
+        <v>40.177</v>
+      </c>
+      <c r="HN4" t="n">
+        <v>43.103</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -3779,9 +3809,18 @@
       <c r="HK5" t="n">
         <v>375.643</v>
       </c>
+      <c r="HL5" t="n">
+        <v>380.204</v>
+      </c>
+      <c r="HM5" t="n">
+        <v>416.095</v>
+      </c>
+      <c r="HN5" t="n">
+        <v>388.346</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -4230,9 +4269,18 @@
       <c r="HK6" t="n">
         <v>6.316</v>
       </c>
+      <c r="HL6" t="n">
+        <v>6.942</v>
+      </c>
+      <c r="HM6" t="n">
+        <v>7.74</v>
+      </c>
+      <c r="HN6" t="n">
+        <v>6.414</v>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -4681,9 +4729,18 @@
       <c r="HK7" t="n">
         <v>61.361</v>
       </c>
+      <c r="HL7" t="n">
+        <v>76.81</v>
+      </c>
+      <c r="HM7" t="n">
+        <v>84.988</v>
+      </c>
+      <c r="HN7" t="n">
+        <v>94.65300000000001</v>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -5132,9 +5189,18 @@
       <c r="HK8" t="n">
         <v>1.032</v>
       </c>
+      <c r="HL8" t="n">
+        <v>1.402</v>
+      </c>
+      <c r="HM8" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="HN8" t="n">
+        <v>1.563</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -5583,9 +5649,18 @@
       <c r="HK9" t="n">
         <v>174.664</v>
       </c>
+      <c r="HL9" t="n">
+        <v>149.028</v>
+      </c>
+      <c r="HM9" t="n">
+        <v>155.93</v>
+      </c>
+      <c r="HN9" t="n">
+        <v>154.007</v>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -6034,9 +6109,18 @@
       <c r="HK10" t="n">
         <v>2.937</v>
       </c>
+      <c r="HL10" t="n">
+        <v>2.721</v>
+      </c>
+      <c r="HM10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="HN10" t="n">
+        <v>2.544</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -6485,9 +6569,18 @@
       <c r="HK11" t="n">
         <v>862.0839999999999</v>
       </c>
+      <c r="HL11" t="n">
+        <v>1078.686</v>
+      </c>
+      <c r="HM11" t="n">
+        <v>1450.311</v>
+      </c>
+      <c r="HN11" t="n">
+        <v>1919.348</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -6936,9 +7029,18 @@
       <c r="HK12" t="n">
         <v>14.495</v>
       </c>
+      <c r="HL12" t="n">
+        <v>19.694</v>
+      </c>
+      <c r="HM12" t="n">
+        <v>26.977</v>
+      </c>
+      <c r="HN12" t="n">
+        <v>31.7</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -7387,9 +7489,18 @@
       <c r="HK13" t="n">
         <v>49.188</v>
       </c>
+      <c r="HL13" t="n">
+        <v>40.436</v>
+      </c>
+      <c r="HM13" t="n">
+        <v>52.689</v>
+      </c>
+      <c r="HN13" t="n">
+        <v>53.394</v>
+      </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -7838,9 +7949,18 @@
       <c r="HK14" t="n">
         <v>0.827</v>
       </c>
+      <c r="HL14" t="n">
+        <v>0.738</v>
+      </c>
+      <c r="HM14" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="HN14" t="n">
+        <v>0.882</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -8289,9 +8409,18 @@
       <c r="HK15" t="n">
         <v>4800.137</v>
       </c>
+      <c r="HL15" t="n">
+        <v>4132.18</v>
+      </c>
+      <c r="HM15" t="n">
+        <v>3632.26</v>
+      </c>
+      <c r="HN15" t="n">
+        <v>3833.327</v>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -8740,9 +8869,18 @@
       <c r="HK16" t="n">
         <v>80.709</v>
       </c>
+      <c r="HL16" t="n">
+        <v>75.444</v>
+      </c>
+      <c r="HM16" t="n">
+        <v>67.562</v>
+      </c>
+      <c r="HN16" t="n">
+        <v>63.311</v>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -9407,9 +9545,18 @@
       <c r="HK17" t="n">
         <v>2783.83</v>
       </c>
+      <c r="HL17" t="n">
+        <v>2534.645</v>
+      </c>
+      <c r="HM17" t="n">
+        <v>2308.62</v>
+      </c>
+      <c r="HN17" t="n">
+        <v>2254.125</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -9882,9 +10029,18 @@
       <c r="HK18" t="n">
         <v>46.807</v>
       </c>
+      <c r="HL18" t="n">
+        <v>46.277</v>
+      </c>
+      <c r="HM18" t="n">
+        <v>42.942</v>
+      </c>
+      <c r="HN18" t="n">
+        <v>37.229</v>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -10333,9 +10489,18 @@
       <c r="HK19" t="n">
         <v>1895.262</v>
       </c>
+      <c r="HL19" t="n">
+        <v>1731.663</v>
+      </c>
+      <c r="HM19" t="n">
+        <v>1480.223</v>
+      </c>
+      <c r="HN19" t="n">
+        <v>1157.725</v>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -10784,9 +10949,18 @@
       <c r="HK20" t="n">
         <v>31.867</v>
       </c>
+      <c r="HL20" t="n">
+        <v>31.616</v>
+      </c>
+      <c r="HM20" t="n">
+        <v>27.533</v>
+      </c>
+      <c r="HN20" t="n">
+        <v>19.121</v>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -11235,9 +11409,18 @@
       <c r="HK21" t="n">
         <v>888.568</v>
       </c>
+      <c r="HL21" t="n">
+        <v>802.982</v>
+      </c>
+      <c r="HM21" t="n">
+        <v>828.397</v>
+      </c>
+      <c r="HN21" t="n">
+        <v>1096.4</v>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -11686,9 +11869,18 @@
       <c r="HK22" t="n">
         <v>14.94</v>
       </c>
+      <c r="HL22" t="n">
+        <v>14.661</v>
+      </c>
+      <c r="HM22" t="n">
+        <v>15.409</v>
+      </c>
+      <c r="HN22" t="n">
+        <v>18.108</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -12137,9 +12329,18 @@
       <c r="HK23" t="n">
         <v>0</v>
       </c>
+      <c r="HL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -12544,9 +12745,12 @@
       <c r="HI24" t="inlineStr"/>
       <c r="HJ24" t="inlineStr"/>
       <c r="HK24" t="inlineStr"/>
+      <c r="HL24" t="inlineStr"/>
+      <c r="HM24" t="inlineStr"/>
+      <c r="HN24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -13209,11 +13413,20 @@
         <v>0</v>
       </c>
       <c r="HK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -13686,9 +13899,18 @@
       <c r="HK26" t="n">
         <v>0</v>
       </c>
+      <c r="HL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -14353,9 +14575,18 @@
       <c r="HK27" t="n">
         <v>1001.569</v>
       </c>
+      <c r="HL27" t="n">
+        <v>748.234</v>
+      </c>
+      <c r="HM27" t="n">
+        <v>599.977</v>
+      </c>
+      <c r="HN27" t="n">
+        <v>745.724</v>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -14828,9 +15059,18 @@
       <c r="HK28" t="n">
         <v>16.84</v>
       </c>
+      <c r="HL28" t="n">
+        <v>13.661</v>
+      </c>
+      <c r="HM28" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="HN28" t="n">
+        <v>12.316</v>
+      </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -15279,9 +15519,18 @@
       <c r="HK29" t="n">
         <v>1001.569</v>
       </c>
+      <c r="HL29" t="n">
+        <v>748.234</v>
+      </c>
+      <c r="HM29" t="n">
+        <v>599.977</v>
+      </c>
+      <c r="HN29" t="n">
+        <v>745.724</v>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -15730,9 +15979,18 @@
       <c r="HK30" t="n">
         <v>16.84</v>
       </c>
+      <c r="HL30" t="n">
+        <v>13.661</v>
+      </c>
+      <c r="HM30" t="n">
+        <v>11.16</v>
+      </c>
+      <c r="HN30" t="n">
+        <v>12.316</v>
+      </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -16181,9 +16439,18 @@
       <c r="HK31" t="n">
         <v>0</v>
       </c>
+      <c r="HL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -16632,9 +16899,18 @@
       <c r="HK32" t="n">
         <v>0</v>
       </c>
+      <c r="HL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -17083,9 +17359,18 @@
       <c r="HK33" t="n">
         <v>639.095</v>
       </c>
+      <c r="HL33" t="n">
+        <v>469.097</v>
+      </c>
+      <c r="HM33" t="n">
+        <v>307.568</v>
+      </c>
+      <c r="HN33" t="n">
+        <v>445.132</v>
+      </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -17534,9 +17819,18 @@
       <c r="HK34" t="n">
         <v>10.746</v>
       </c>
+      <c r="HL34" t="n">
+        <v>8.565</v>
+      </c>
+      <c r="HM34" t="n">
+        <v>5.721</v>
+      </c>
+      <c r="HN34" t="n">
+        <v>7.352</v>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -17985,9 +18279,18 @@
       <c r="HK35" t="n">
         <v>0</v>
       </c>
+      <c r="HL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -18436,9 +18739,18 @@
       <c r="HK36" t="n">
         <v>0</v>
       </c>
+      <c r="HL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -18887,9 +19199,18 @@
       <c r="HK37" t="n">
         <v>639.095</v>
       </c>
+      <c r="HL37" t="n">
+        <v>469.097</v>
+      </c>
+      <c r="HM37" t="n">
+        <v>307.568</v>
+      </c>
+      <c r="HN37" t="n">
+        <v>445.132</v>
+      </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -19338,9 +19659,18 @@
       <c r="HK38" t="n">
         <v>10.746</v>
       </c>
+      <c r="HL38" t="n">
+        <v>8.565</v>
+      </c>
+      <c r="HM38" t="n">
+        <v>5.721</v>
+      </c>
+      <c r="HN38" t="n">
+        <v>7.352</v>
+      </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -19789,9 +20119,18 @@
       <c r="HK39" t="n">
         <v>0</v>
       </c>
+      <c r="HL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -20240,9 +20579,18 @@
       <c r="HK40" t="n">
         <v>0</v>
       </c>
+      <c r="HL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -20905,11 +21253,20 @@
         <v>0</v>
       </c>
       <c r="HK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN41" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -21382,9 +21739,18 @@
       <c r="HK42" t="n">
         <v>0</v>
       </c>
+      <c r="HL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -21833,9 +22199,18 @@
       <c r="HK43" t="n">
         <v>0</v>
       </c>
+      <c r="HL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -22284,9 +22659,18 @@
       <c r="HK44" t="n">
         <v>0</v>
       </c>
+      <c r="HL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -22567,9 +22951,18 @@
       <c r="HK45" t="n">
         <v>1147.297</v>
       </c>
+      <c r="HL45" t="n">
+        <v>1344.96</v>
+      </c>
+      <c r="HM45" t="n">
+        <v>1743.918</v>
+      </c>
+      <c r="HN45" t="n">
+        <v>2221.402</v>
+      </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -22850,6 +23243,15 @@
       <c r="HK46" t="n">
         <v>19.291</v>
       </c>
+      <c r="HL46" t="n">
+        <v>24.556</v>
+      </c>
+      <c r="HM46" t="n">
+        <v>32.438</v>
+      </c>
+      <c r="HN46" t="n">
+        <v>36.689</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
+++ b/services/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HN46"/>
+  <dimension ref="A1:HO46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1522,6 +1522,11 @@
           <t>2026-01</t>
         </is>
       </c>
+      <c r="HO1" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2197,6 +2202,9 @@
       </c>
       <c r="HN2" t="n">
         <v>6054.729</v>
+      </c>
+      <c r="HO2" t="n">
+        <v>5604.233</v>
       </c>
     </row>
     <row r="3">
@@ -2873,6 +2881,9 @@
       </c>
       <c r="HN3" t="n">
         <v>2609.748</v>
+      </c>
+      <c r="HO3" t="n">
+        <v>2101.715</v>
       </c>
     </row>
     <row r="4">
@@ -3357,6 +3368,9 @@
       </c>
       <c r="HN4" t="n">
         <v>43.103</v>
+      </c>
+      <c r="HO4" t="n">
+        <v>37.502</v>
       </c>
     </row>
     <row r="5">
@@ -3818,6 +3832,9 @@
       <c r="HN5" t="n">
         <v>388.346</v>
       </c>
+      <c r="HO5" t="n">
+        <v>333.765</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4278,6 +4295,9 @@
       <c r="HN6" t="n">
         <v>6.414</v>
       </c>
+      <c r="HO6" t="n">
+        <v>5.956</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4738,6 +4758,9 @@
       <c r="HN7" t="n">
         <v>94.65300000000001</v>
       </c>
+      <c r="HO7" t="n">
+        <v>71.91500000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5198,6 +5221,9 @@
       <c r="HN8" t="n">
         <v>1.563</v>
       </c>
+      <c r="HO8" t="n">
+        <v>1.283</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5658,6 +5684,9 @@
       <c r="HN9" t="n">
         <v>154.007</v>
       </c>
+      <c r="HO9" t="n">
+        <v>129.16</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6118,6 +6147,9 @@
       <c r="HN10" t="n">
         <v>2.544</v>
       </c>
+      <c r="HO10" t="n">
+        <v>2.305</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6578,6 +6610,9 @@
       <c r="HN11" t="n">
         <v>1919.348</v>
       </c>
+      <c r="HO11" t="n">
+        <v>1518.227</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7038,6 +7073,9 @@
       <c r="HN12" t="n">
         <v>31.7</v>
       </c>
+      <c r="HO12" t="n">
+        <v>27.091</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7498,6 +7536,9 @@
       <c r="HN13" t="n">
         <v>53.394</v>
       </c>
+      <c r="HO13" t="n">
+        <v>48.648</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -7958,6 +7999,9 @@
       <c r="HN14" t="n">
         <v>0.882</v>
       </c>
+      <c r="HO14" t="n">
+        <v>0.868</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8418,6 +8462,9 @@
       <c r="HN15" t="n">
         <v>3833.327</v>
       </c>
+      <c r="HO15" t="n">
+        <v>3836.283</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8878,6 +8925,9 @@
       <c r="HN16" t="n">
         <v>63.311</v>
       </c>
+      <c r="HO16" t="n">
+        <v>68.453</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9553,6 +9603,9 @@
       </c>
       <c r="HN17" t="n">
         <v>2254.125</v>
+      </c>
+      <c r="HO17" t="n">
+        <v>2259.283</v>
       </c>
     </row>
     <row r="18">
@@ -10037,6 +10090,9 @@
       </c>
       <c r="HN18" t="n">
         <v>37.229</v>
+      </c>
+      <c r="HO18" t="n">
+        <v>40.314</v>
       </c>
     </row>
     <row r="19">
@@ -10498,6 +10554,9 @@
       <c r="HN19" t="n">
         <v>1157.725</v>
       </c>
+      <c r="HO19" t="n">
+        <v>1511.926</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -10958,6 +11017,9 @@
       <c r="HN20" t="n">
         <v>19.121</v>
       </c>
+      <c r="HO20" t="n">
+        <v>26.978</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11418,6 +11480,9 @@
       <c r="HN21" t="n">
         <v>1096.4</v>
       </c>
+      <c r="HO21" t="n">
+        <v>747.357</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11878,6 +11943,9 @@
       <c r="HN22" t="n">
         <v>18.108</v>
       </c>
+      <c r="HO22" t="n">
+        <v>13.336</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12338,6 +12406,9 @@
       <c r="HN23" t="n">
         <v>0</v>
       </c>
+      <c r="HO23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12748,6 +12819,7 @@
       <c r="HL24" t="inlineStr"/>
       <c r="HM24" t="inlineStr"/>
       <c r="HN24" t="inlineStr"/>
+      <c r="HO24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -13422,6 +13494,9 @@
         <v>0</v>
       </c>
       <c r="HN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13908,6 +13983,9 @@
       <c r="HN26" t="n">
         <v>0</v>
       </c>
+      <c r="HO26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -14583,6 +14661,9 @@
       </c>
       <c r="HN27" t="n">
         <v>745.724</v>
+      </c>
+      <c r="HO27" t="n">
+        <v>745.259</v>
       </c>
     </row>
     <row r="28">
@@ -15067,6 +15148,9 @@
       </c>
       <c r="HN28" t="n">
         <v>12.316</v>
+      </c>
+      <c r="HO28" t="n">
+        <v>13.298</v>
       </c>
     </row>
     <row r="29">
@@ -15528,6 +15612,9 @@
       <c r="HN29" t="n">
         <v>745.724</v>
       </c>
+      <c r="HO29" t="n">
+        <v>745.259</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -15988,6 +16075,9 @@
       <c r="HN30" t="n">
         <v>12.316</v>
       </c>
+      <c r="HO30" t="n">
+        <v>13.298</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -16448,6 +16538,9 @@
       <c r="HN31" t="n">
         <v>0</v>
       </c>
+      <c r="HO31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -16908,6 +17001,9 @@
       <c r="HN32" t="n">
         <v>0</v>
       </c>
+      <c r="HO32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -17368,6 +17464,9 @@
       <c r="HN33" t="n">
         <v>445.132</v>
       </c>
+      <c r="HO33" t="n">
+        <v>497.976</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -17828,6 +17927,9 @@
       <c r="HN34" t="n">
         <v>7.352</v>
       </c>
+      <c r="HO34" t="n">
+        <v>8.885999999999999</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -18288,6 +18390,9 @@
       <c r="HN35" t="n">
         <v>0</v>
       </c>
+      <c r="HO35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -18748,6 +18853,9 @@
       <c r="HN36" t="n">
         <v>0</v>
       </c>
+      <c r="HO36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -19208,6 +19316,9 @@
       <c r="HN37" t="n">
         <v>445.132</v>
       </c>
+      <c r="HO37" t="n">
+        <v>497.976</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -19668,6 +19779,9 @@
       <c r="HN38" t="n">
         <v>7.352</v>
       </c>
+      <c r="HO38" t="n">
+        <v>8.885999999999999</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -20128,6 +20242,9 @@
       <c r="HN39" t="n">
         <v>0</v>
       </c>
+      <c r="HO39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -20588,6 +20705,9 @@
       <c r="HN40" t="n">
         <v>0</v>
       </c>
+      <c r="HO40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -21262,6 +21382,9 @@
         <v>0</v>
       </c>
       <c r="HN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -21746,6 +21869,9 @@
         <v>0</v>
       </c>
       <c r="HN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO42" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22208,6 +22334,9 @@
       <c r="HN43" t="n">
         <v>0</v>
       </c>
+      <c r="HO43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -22666,6 +22795,9 @@
         <v>0</v>
       </c>
       <c r="HN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO44" t="n">
         <v>0</v>
       </c>
     </row>
@@ -22960,6 +23092,9 @@
       <c r="HN45" t="n">
         <v>2221.402</v>
       </c>
+      <c r="HO45" t="n">
+        <v>1767.95</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -23252,6 +23387,9 @@
       <c r="HN46" t="n">
         <v>36.689</v>
       </c>
+      <c r="HO46" t="n">
+        <v>31.547</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
+++ b/services/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HO46"/>
+  <dimension ref="A1:HP46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1527,6 +1527,11 @@
           <t>2026-02</t>
         </is>
       </c>
+      <c r="HP1" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2206,6 +2211,7 @@
       <c r="HO2" t="n">
         <v>5604.233</v>
       </c>
+      <c r="HP2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2885,6 +2891,7 @@
       <c r="HO3" t="n">
         <v>2101.715</v>
       </c>
+      <c r="HP3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3372,6 +3379,7 @@
       <c r="HO4" t="n">
         <v>37.502</v>
       </c>
+      <c r="HP4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3835,6 +3843,7 @@
       <c r="HO5" t="n">
         <v>333.765</v>
       </c>
+      <c r="HP5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4298,6 +4307,7 @@
       <c r="HO6" t="n">
         <v>5.956</v>
       </c>
+      <c r="HP6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4761,6 +4771,7 @@
       <c r="HO7" t="n">
         <v>71.91500000000001</v>
       </c>
+      <c r="HP7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5224,6 +5235,7 @@
       <c r="HO8" t="n">
         <v>1.283</v>
       </c>
+      <c r="HP8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5687,6 +5699,7 @@
       <c r="HO9" t="n">
         <v>129.16</v>
       </c>
+      <c r="HP9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6150,6 +6163,7 @@
       <c r="HO10" t="n">
         <v>2.305</v>
       </c>
+      <c r="HP10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6613,6 +6627,7 @@
       <c r="HO11" t="n">
         <v>1518.227</v>
       </c>
+      <c r="HP11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7076,6 +7091,7 @@
       <c r="HO12" t="n">
         <v>27.091</v>
       </c>
+      <c r="HP12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7539,6 +7555,7 @@
       <c r="HO13" t="n">
         <v>48.648</v>
       </c>
+      <c r="HP13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8002,6 +8019,7 @@
       <c r="HO14" t="n">
         <v>0.868</v>
       </c>
+      <c r="HP14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8465,6 +8483,7 @@
       <c r="HO15" t="n">
         <v>3836.283</v>
       </c>
+      <c r="HP15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8928,6 +8947,7 @@
       <c r="HO16" t="n">
         <v>68.453</v>
       </c>
+      <c r="HP16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9607,6 +9627,7 @@
       <c r="HO17" t="n">
         <v>2259.283</v>
       </c>
+      <c r="HP17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10094,6 +10115,7 @@
       <c r="HO18" t="n">
         <v>40.314</v>
       </c>
+      <c r="HP18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10557,6 +10579,7 @@
       <c r="HO19" t="n">
         <v>1511.926</v>
       </c>
+      <c r="HP19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11020,6 +11043,7 @@
       <c r="HO20" t="n">
         <v>26.978</v>
       </c>
+      <c r="HP20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11483,6 +11507,7 @@
       <c r="HO21" t="n">
         <v>747.357</v>
       </c>
+      <c r="HP21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11946,6 +11971,7 @@
       <c r="HO22" t="n">
         <v>13.336</v>
       </c>
+      <c r="HP22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12409,6 +12435,7 @@
       <c r="HO23" t="n">
         <v>0</v>
       </c>
+      <c r="HP23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12820,6 +12847,7 @@
       <c r="HM24" t="inlineStr"/>
       <c r="HN24" t="inlineStr"/>
       <c r="HO24" t="inlineStr"/>
+      <c r="HP24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -13499,6 +13527,7 @@
       <c r="HO25" t="n">
         <v>0</v>
       </c>
+      <c r="HP25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -13986,6 +14015,7 @@
       <c r="HO26" t="n">
         <v>0</v>
       </c>
+      <c r="HP26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -14665,6 +14695,7 @@
       <c r="HO27" t="n">
         <v>745.259</v>
       </c>
+      <c r="HP27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -15152,6 +15183,7 @@
       <c r="HO28" t="n">
         <v>13.298</v>
       </c>
+      <c r="HP28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -15615,6 +15647,7 @@
       <c r="HO29" t="n">
         <v>745.259</v>
       </c>
+      <c r="HP29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -16078,6 +16111,7 @@
       <c r="HO30" t="n">
         <v>13.298</v>
       </c>
+      <c r="HP30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -16541,6 +16575,7 @@
       <c r="HO31" t="n">
         <v>0</v>
       </c>
+      <c r="HP31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -17004,6 +17039,7 @@
       <c r="HO32" t="n">
         <v>0</v>
       </c>
+      <c r="HP32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -17467,6 +17503,7 @@
       <c r="HO33" t="n">
         <v>497.976</v>
       </c>
+      <c r="HP33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -17930,6 +17967,7 @@
       <c r="HO34" t="n">
         <v>8.885999999999999</v>
       </c>
+      <c r="HP34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -18393,6 +18431,7 @@
       <c r="HO35" t="n">
         <v>0</v>
       </c>
+      <c r="HP35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -18856,6 +18895,7 @@
       <c r="HO36" t="n">
         <v>0</v>
       </c>
+      <c r="HP36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -19319,6 +19359,7 @@
       <c r="HO37" t="n">
         <v>497.976</v>
       </c>
+      <c r="HP37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -19782,6 +19823,7 @@
       <c r="HO38" t="n">
         <v>8.885999999999999</v>
       </c>
+      <c r="HP38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -20245,6 +20287,7 @@
       <c r="HO39" t="n">
         <v>0</v>
       </c>
+      <c r="HP39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -20708,6 +20751,7 @@
       <c r="HO40" t="n">
         <v>0</v>
       </c>
+      <c r="HP40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -21387,6 +21431,7 @@
       <c r="HO41" t="n">
         <v>0</v>
       </c>
+      <c r="HP41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -21874,6 +21919,7 @@
       <c r="HO42" t="n">
         <v>0</v>
       </c>
+      <c r="HP42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -22337,6 +22383,7 @@
       <c r="HO43" t="n">
         <v>0</v>
       </c>
+      <c r="HP43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -22800,6 +22847,7 @@
       <c r="HO44" t="n">
         <v>0</v>
       </c>
+      <c r="HP44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -23095,6 +23143,7 @@
       <c r="HO45" t="n">
         <v>1767.95</v>
       </c>
+      <c r="HP45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -23390,6 +23439,7 @@
       <c r="HO46" t="n">
         <v>31.547</v>
       </c>
+      <c r="HP46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
+++ b/services/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
@@ -2211,7 +2211,9 @@
       <c r="HO2" t="n">
         <v>5604.233</v>
       </c>
-      <c r="HP2" t="inlineStr"/>
+      <c r="HP2" t="n">
+        <v>5973.698</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2891,7 +2893,9 @@
       <c r="HO3" t="n">
         <v>2101.715</v>
       </c>
-      <c r="HP3" t="inlineStr"/>
+      <c r="HP3" t="n">
+        <v>1384.772</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3379,7 +3383,9 @@
       <c r="HO4" t="n">
         <v>37.502</v>
       </c>
-      <c r="HP4" t="inlineStr"/>
+      <c r="HP4" t="n">
+        <v>23.181</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3843,7 +3849,9 @@
       <c r="HO5" t="n">
         <v>333.765</v>
       </c>
-      <c r="HP5" t="inlineStr"/>
+      <c r="HP5" t="n">
+        <v>377.647</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4307,7 +4315,9 @@
       <c r="HO6" t="n">
         <v>5.956</v>
       </c>
-      <c r="HP6" t="inlineStr"/>
+      <c r="HP6" t="n">
+        <v>6.322</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4771,7 +4781,9 @@
       <c r="HO7" t="n">
         <v>71.91500000000001</v>
       </c>
-      <c r="HP7" t="inlineStr"/>
+      <c r="HP7" t="n">
+        <v>70.504</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -5235,7 +5247,9 @@
       <c r="HO8" t="n">
         <v>1.283</v>
       </c>
-      <c r="HP8" t="inlineStr"/>
+      <c r="HP8" t="n">
+        <v>1.18</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5699,7 +5713,9 @@
       <c r="HO9" t="n">
         <v>129.16</v>
       </c>
-      <c r="HP9" t="inlineStr"/>
+      <c r="HP9" t="n">
+        <v>151.223</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6163,7 +6179,9 @@
       <c r="HO10" t="n">
         <v>2.305</v>
       </c>
-      <c r="HP10" t="inlineStr"/>
+      <c r="HP10" t="n">
+        <v>2.531</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6627,7 +6645,9 @@
       <c r="HO11" t="n">
         <v>1518.227</v>
       </c>
-      <c r="HP11" t="inlineStr"/>
+      <c r="HP11" t="n">
+        <v>752.622</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7091,7 +7111,9 @@
       <c r="HO12" t="n">
         <v>27.091</v>
       </c>
-      <c r="HP12" t="inlineStr"/>
+      <c r="HP12" t="n">
+        <v>12.599</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7555,7 +7577,9 @@
       <c r="HO13" t="n">
         <v>48.648</v>
       </c>
-      <c r="HP13" t="inlineStr"/>
+      <c r="HP13" t="n">
+        <v>32.776</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8019,7 +8043,9 @@
       <c r="HO14" t="n">
         <v>0.868</v>
       </c>
-      <c r="HP14" t="inlineStr"/>
+      <c r="HP14" t="n">
+        <v>0.549</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8483,7 +8509,9 @@
       <c r="HO15" t="n">
         <v>3836.283</v>
       </c>
-      <c r="HP15" t="inlineStr"/>
+      <c r="HP15" t="n">
+        <v>4966.573</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8947,7 +8975,9 @@
       <c r="HO16" t="n">
         <v>68.453</v>
       </c>
-      <c r="HP16" t="inlineStr"/>
+      <c r="HP16" t="n">
+        <v>83.14100000000001</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9627,7 +9657,9 @@
       <c r="HO17" t="n">
         <v>2259.283</v>
       </c>
-      <c r="HP17" t="inlineStr"/>
+      <c r="HP17" t="n">
+        <v>2650.601</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10115,7 +10147,9 @@
       <c r="HO18" t="n">
         <v>40.314</v>
       </c>
-      <c r="HP18" t="inlineStr"/>
+      <c r="HP18" t="n">
+        <v>44.371</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10579,7 +10613,9 @@
       <c r="HO19" t="n">
         <v>1511.926</v>
       </c>
-      <c r="HP19" t="inlineStr"/>
+      <c r="HP19" t="n">
+        <v>1611.632</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11043,7 +11079,9 @@
       <c r="HO20" t="n">
         <v>26.978</v>
       </c>
-      <c r="HP20" t="inlineStr"/>
+      <c r="HP20" t="n">
+        <v>26.979</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11507,7 +11545,9 @@
       <c r="HO21" t="n">
         <v>747.357</v>
       </c>
-      <c r="HP21" t="inlineStr"/>
+      <c r="HP21" t="n">
+        <v>1038.969</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -11971,7 +12011,9 @@
       <c r="HO22" t="n">
         <v>13.336</v>
       </c>
-      <c r="HP22" t="inlineStr"/>
+      <c r="HP22" t="n">
+        <v>17.392</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12435,7 +12477,9 @@
       <c r="HO23" t="n">
         <v>0</v>
       </c>
-      <c r="HP23" t="inlineStr"/>
+      <c r="HP23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -13527,7 +13571,9 @@
       <c r="HO25" t="n">
         <v>0</v>
       </c>
-      <c r="HP25" t="inlineStr"/>
+      <c r="HP25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -14015,7 +14061,9 @@
       <c r="HO26" t="n">
         <v>0</v>
       </c>
-      <c r="HP26" t="inlineStr"/>
+      <c r="HP26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -14695,7 +14743,9 @@
       <c r="HO27" t="n">
         <v>745.259</v>
       </c>
-      <c r="HP27" t="inlineStr"/>
+      <c r="HP27" t="n">
+        <v>968.135</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -15183,7 +15233,9 @@
       <c r="HO28" t="n">
         <v>13.298</v>
       </c>
-      <c r="HP28" t="inlineStr"/>
+      <c r="HP28" t="n">
+        <v>16.207</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -15647,7 +15699,9 @@
       <c r="HO29" t="n">
         <v>745.259</v>
       </c>
-      <c r="HP29" t="inlineStr"/>
+      <c r="HP29" t="n">
+        <v>968.135</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -16111,7 +16165,9 @@
       <c r="HO30" t="n">
         <v>13.298</v>
       </c>
-      <c r="HP30" t="inlineStr"/>
+      <c r="HP30" t="n">
+        <v>16.207</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -16575,7 +16631,9 @@
       <c r="HO31" t="n">
         <v>0</v>
       </c>
-      <c r="HP31" t="inlineStr"/>
+      <c r="HP31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -17039,7 +17097,9 @@
       <c r="HO32" t="n">
         <v>0</v>
       </c>
-      <c r="HP32" t="inlineStr"/>
+      <c r="HP32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -17503,7 +17563,9 @@
       <c r="HO33" t="n">
         <v>497.976</v>
       </c>
-      <c r="HP33" t="inlineStr"/>
+      <c r="HP33" t="n">
+        <v>970.1900000000001</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -17967,7 +18029,9 @@
       <c r="HO34" t="n">
         <v>8.885999999999999</v>
       </c>
-      <c r="HP34" t="inlineStr"/>
+      <c r="HP34" t="n">
+        <v>16.241</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -18431,7 +18495,9 @@
       <c r="HO35" t="n">
         <v>0</v>
       </c>
-      <c r="HP35" t="inlineStr"/>
+      <c r="HP35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -18895,7 +18961,9 @@
       <c r="HO36" t="n">
         <v>0</v>
       </c>
-      <c r="HP36" t="inlineStr"/>
+      <c r="HP36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -19359,7 +19427,9 @@
       <c r="HO37" t="n">
         <v>497.976</v>
       </c>
-      <c r="HP37" t="inlineStr"/>
+      <c r="HP37" t="n">
+        <v>970.1900000000001</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -19823,7 +19893,9 @@
       <c r="HO38" t="n">
         <v>8.885999999999999</v>
       </c>
-      <c r="HP38" t="inlineStr"/>
+      <c r="HP38" t="n">
+        <v>16.241</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -20287,7 +20359,9 @@
       <c r="HO39" t="n">
         <v>0</v>
       </c>
-      <c r="HP39" t="inlineStr"/>
+      <c r="HP39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -20751,7 +20825,9 @@
       <c r="HO40" t="n">
         <v>0</v>
       </c>
-      <c r="HP40" t="inlineStr"/>
+      <c r="HP40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -21431,7 +21507,9 @@
       <c r="HO41" t="n">
         <v>0</v>
       </c>
-      <c r="HP41" t="inlineStr"/>
+      <c r="HP41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -21919,7 +21997,9 @@
       <c r="HO42" t="n">
         <v>0</v>
       </c>
-      <c r="HP42" t="inlineStr"/>
+      <c r="HP42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -22383,7 +22463,9 @@
       <c r="HO43" t="n">
         <v>0</v>
       </c>
-      <c r="HP43" t="inlineStr"/>
+      <c r="HP43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -22847,7 +22929,9 @@
       <c r="HO44" t="n">
         <v>0</v>
       </c>
-      <c r="HP44" t="inlineStr"/>
+      <c r="HP44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -23143,7 +23227,9 @@
       <c r="HO45" t="n">
         <v>1767.95</v>
       </c>
-      <c r="HP45" t="inlineStr"/>
+      <c r="HP45" t="n">
+        <v>1007.125</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -23439,7 +23525,9 @@
       <c r="HO46" t="n">
         <v>31.547</v>
       </c>
-      <c r="HP46" t="inlineStr"/>
+      <c r="HP46" t="n">
+        <v>16.859</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/services/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
+++ b/services/data_raw/eurostat/AT_electricity_fuel_type_nrg_cb_pem.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:HP46"/>
+  <dimension ref="A1:HS46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1532,6 +1532,21 @@
           <t>2026-03</t>
         </is>
       </c>
+      <c r="HQ1" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="HR1" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="HS1" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2214,6 +2229,13 @@
       <c r="HP2" t="n">
         <v>5973.698</v>
       </c>
+      <c r="HQ2" t="n">
+        <v>5977.32</v>
+      </c>
+      <c r="HR2" t="n">
+        <v>6011.108</v>
+      </c>
+      <c r="HS2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2896,6 +2918,13 @@
       <c r="HP3" t="n">
         <v>1384.772</v>
       </c>
+      <c r="HQ3" t="n">
+        <v>1156.266</v>
+      </c>
+      <c r="HR3" t="n">
+        <v>696.495</v>
+      </c>
+      <c r="HS3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -3386,6 +3415,13 @@
       <c r="HP4" t="n">
         <v>23.181</v>
       </c>
+      <c r="HQ4" t="n">
+        <v>19.344</v>
+      </c>
+      <c r="HR4" t="n">
+        <v>11.587</v>
+      </c>
+      <c r="HS4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -3852,6 +3888,13 @@
       <c r="HP5" t="n">
         <v>377.647</v>
       </c>
+      <c r="HQ5" t="n">
+        <v>332.233</v>
+      </c>
+      <c r="HR5" t="n">
+        <v>317.278</v>
+      </c>
+      <c r="HS5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -4318,6 +4361,13 @@
       <c r="HP6" t="n">
         <v>6.322</v>
       </c>
+      <c r="HQ6" t="n">
+        <v>5.558</v>
+      </c>
+      <c r="HR6" t="n">
+        <v>5.278</v>
+      </c>
+      <c r="HS6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -4330,7 +4380,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Combustible fuels - non-renewable [CF_NR]</t>
+          <t>Combustible fuels - non-renewable - other [CF_NR_OTH]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -4784,6 +4834,13 @@
       <c r="HP7" t="n">
         <v>70.504</v>
       </c>
+      <c r="HQ7" t="n">
+        <v>62.647</v>
+      </c>
+      <c r="HR7" t="n">
+        <v>55.011</v>
+      </c>
+      <c r="HS7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -4796,7 +4853,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Combustible fuels - non-renewable [CF_NR]</t>
+          <t>Combustible fuels - non-renewable - other [CF_NR_OTH]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -4917,222 +4974,78 @@
       <c r="DG8" t="inlineStr"/>
       <c r="DH8" t="inlineStr"/>
       <c r="DI8" t="inlineStr"/>
-      <c r="DJ8" t="n">
-        <v>1.195</v>
-      </c>
-      <c r="DK8" t="n">
-        <v>1.237</v>
-      </c>
-      <c r="DL8" t="n">
-        <v>0.994</v>
-      </c>
-      <c r="DM8" t="n">
-        <v>1.132</v>
-      </c>
-      <c r="DN8" t="n">
-        <v>1.155</v>
-      </c>
-      <c r="DO8" t="n">
-        <v>1.205</v>
-      </c>
-      <c r="DP8" t="n">
-        <v>1.207</v>
-      </c>
-      <c r="DQ8" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="DR8" t="n">
-        <v>0.8169999999999999</v>
-      </c>
-      <c r="DS8" t="n">
-        <v>0.988</v>
-      </c>
-      <c r="DT8" t="n">
-        <v>1.141</v>
-      </c>
-      <c r="DU8" t="n">
-        <v>1.094</v>
-      </c>
-      <c r="DV8" t="n">
-        <v>0.923</v>
-      </c>
-      <c r="DW8" t="n">
-        <v>1.117</v>
-      </c>
-      <c r="DX8" t="n">
-        <v>1.084</v>
-      </c>
-      <c r="DY8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="DZ8" t="n">
-        <v>1.066</v>
-      </c>
-      <c r="EA8" t="n">
-        <v>1.066</v>
-      </c>
-      <c r="EB8" t="n">
-        <v>1.147</v>
-      </c>
-      <c r="EC8" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="ED8" t="n">
-        <v>1.051</v>
-      </c>
-      <c r="EE8" t="n">
-        <v>1.005</v>
-      </c>
-      <c r="EF8" t="n">
-        <v>1.113</v>
-      </c>
-      <c r="EG8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="EH8" t="n">
-        <v>1.085</v>
-      </c>
-      <c r="EI8" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="EJ8" t="n">
-        <v>0.966</v>
-      </c>
-      <c r="EK8" t="n">
-        <v>1.093</v>
-      </c>
-      <c r="EL8" t="n">
-        <v>1.004</v>
-      </c>
-      <c r="EM8" t="n">
-        <v>0.851</v>
-      </c>
-      <c r="EN8" t="n">
-        <v>1.099</v>
-      </c>
-      <c r="EO8" t="n">
-        <v>1.056</v>
-      </c>
-      <c r="EP8" t="n">
-        <v>1.068</v>
-      </c>
-      <c r="EQ8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="ER8" t="n">
-        <v>1.188</v>
-      </c>
-      <c r="ES8" t="n">
-        <v>1.234</v>
-      </c>
-      <c r="ET8" t="n">
-        <v>0.997</v>
-      </c>
-      <c r="EU8" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="EV8" t="n">
-        <v>0.746</v>
-      </c>
-      <c r="EW8" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="EX8" t="n">
-        <v>0.766</v>
-      </c>
-      <c r="EY8" t="n">
-        <v>0.647</v>
-      </c>
-      <c r="EZ8" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="FA8" t="n">
-        <v>0.749</v>
-      </c>
-      <c r="FB8" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="FC8" t="n">
-        <v>0.797</v>
-      </c>
-      <c r="FD8" t="n">
-        <v>0.978</v>
-      </c>
-      <c r="FE8" t="n">
-        <v>0.957</v>
-      </c>
-      <c r="FF8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="FG8" t="n">
-        <v>0.929</v>
-      </c>
-      <c r="FH8" t="n">
-        <v>0.794</v>
-      </c>
-      <c r="FI8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="FJ8" t="n">
-        <v>0.738</v>
-      </c>
-      <c r="FK8" t="n">
-        <v>0.639</v>
-      </c>
-      <c r="FL8" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="FM8" t="n">
-        <v>0.681</v>
-      </c>
-      <c r="FN8" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="FO8" t="n">
-        <v>0.826</v>
-      </c>
-      <c r="FP8" t="n">
-        <v>0.947</v>
-      </c>
-      <c r="FQ8" t="n">
-        <v>1.121</v>
-      </c>
-      <c r="FR8" t="n">
-        <v>0.864</v>
-      </c>
-      <c r="FS8" t="n">
-        <v>0.973</v>
-      </c>
-      <c r="FT8" t="n">
-        <v>0.837</v>
-      </c>
-      <c r="FU8" t="n">
-        <v>0.739</v>
-      </c>
-      <c r="FV8" t="n">
-        <v>0.906</v>
-      </c>
-      <c r="FW8" t="n">
-        <v>0.873</v>
-      </c>
-      <c r="FX8" t="n">
-        <v>0.847</v>
-      </c>
-      <c r="FY8" t="n">
-        <v>1.063</v>
-      </c>
-      <c r="FZ8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="GA8" t="n">
-        <v>0.992</v>
-      </c>
-      <c r="GB8" t="n">
-        <v>1.132</v>
-      </c>
-      <c r="GC8" t="n">
-        <v>1.049</v>
-      </c>
+      <c r="DJ8" t="inlineStr"/>
+      <c r="DK8" t="inlineStr"/>
+      <c r="DL8" t="inlineStr"/>
+      <c r="DM8" t="inlineStr"/>
+      <c r="DN8" t="inlineStr"/>
+      <c r="DO8" t="inlineStr"/>
+      <c r="DP8" t="inlineStr"/>
+      <c r="DQ8" t="inlineStr"/>
+      <c r="DR8" t="inlineStr"/>
+      <c r="DS8" t="inlineStr"/>
+      <c r="DT8" t="inlineStr"/>
+      <c r="DU8" t="inlineStr"/>
+      <c r="DV8" t="inlineStr"/>
+      <c r="DW8" t="inlineStr"/>
+      <c r="DX8" t="inlineStr"/>
+      <c r="DY8" t="inlineStr"/>
+      <c r="DZ8" t="inlineStr"/>
+      <c r="EA8" t="inlineStr"/>
+      <c r="EB8" t="inlineStr"/>
+      <c r="EC8" t="inlineStr"/>
+      <c r="ED8" t="inlineStr"/>
+      <c r="EE8" t="inlineStr"/>
+      <c r="EF8" t="inlineStr"/>
+      <c r="EG8" t="inlineStr"/>
+      <c r="EH8" t="inlineStr"/>
+      <c r="EI8" t="inlineStr"/>
+      <c r="EJ8" t="inlineStr"/>
+      <c r="EK8" t="inlineStr"/>
+      <c r="EL8" t="inlineStr"/>
+      <c r="EM8" t="inlineStr"/>
+      <c r="EN8" t="inlineStr"/>
+      <c r="EO8" t="inlineStr"/>
+      <c r="EP8" t="inlineStr"/>
+      <c r="EQ8" t="inlineStr"/>
+      <c r="ER8" t="inlineStr"/>
+      <c r="ES8" t="inlineStr"/>
+      <c r="ET8" t="inlineStr"/>
+      <c r="EU8" t="inlineStr"/>
+      <c r="EV8" t="inlineStr"/>
+      <c r="EW8" t="inlineStr"/>
+      <c r="EX8" t="inlineStr"/>
+      <c r="EY8" t="inlineStr"/>
+      <c r="EZ8" t="inlineStr"/>
+      <c r="FA8" t="inlineStr"/>
+      <c r="FB8" t="inlineStr"/>
+      <c r="FC8" t="inlineStr"/>
+      <c r="FD8" t="inlineStr"/>
+      <c r="FE8" t="inlineStr"/>
+      <c r="FF8" t="inlineStr"/>
+      <c r="FG8" t="inlineStr"/>
+      <c r="FH8" t="inlineStr"/>
+      <c r="FI8" t="inlineStr"/>
+      <c r="FJ8" t="inlineStr"/>
+      <c r="FK8" t="inlineStr"/>
+      <c r="FL8" t="inlineStr"/>
+      <c r="FM8" t="inlineStr"/>
+      <c r="FN8" t="inlineStr"/>
+      <c r="FO8" t="inlineStr"/>
+      <c r="FP8" t="inlineStr"/>
+      <c r="FQ8" t="inlineStr"/>
+      <c r="FR8" t="inlineStr"/>
+      <c r="FS8" t="inlineStr"/>
+      <c r="FT8" t="inlineStr"/>
+      <c r="FU8" t="inlineStr"/>
+      <c r="FV8" t="inlineStr"/>
+      <c r="FW8" t="inlineStr"/>
+      <c r="FX8" t="inlineStr"/>
+      <c r="FY8" t="inlineStr"/>
+      <c r="FZ8" t="inlineStr"/>
+      <c r="GA8" t="inlineStr"/>
+      <c r="GB8" t="inlineStr"/>
+      <c r="GC8" t="inlineStr"/>
       <c r="GD8" t="n">
         <v>1.118</v>
       </c>
@@ -5169,27 +5082,13 @@
       <c r="GO8" t="n">
         <v>0.806</v>
       </c>
-      <c r="GP8" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="GQ8" t="n">
-        <v>0.8080000000000001</v>
-      </c>
-      <c r="GR8" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="GS8" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="GT8" t="n">
-        <v>0.574</v>
-      </c>
-      <c r="GU8" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="GV8" t="n">
-        <v>0.714</v>
-      </c>
+      <c r="GP8" t="inlineStr"/>
+      <c r="GQ8" t="inlineStr"/>
+      <c r="GR8" t="inlineStr"/>
+      <c r="GS8" t="inlineStr"/>
+      <c r="GT8" t="inlineStr"/>
+      <c r="GU8" t="inlineStr"/>
+      <c r="GV8" t="inlineStr"/>
       <c r="GW8" t="n">
         <v>0.796</v>
       </c>
@@ -5250,6 +5149,13 @@
       <c r="HP8" t="n">
         <v>1.18</v>
       </c>
+      <c r="HQ8" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="HR8" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="HS8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -5716,6 +5622,13 @@
       <c r="HP9" t="n">
         <v>151.223</v>
       </c>
+      <c r="HQ9" t="n">
+        <v>134.276</v>
+      </c>
+      <c r="HR9" t="n">
+        <v>140.202</v>
+      </c>
+      <c r="HS9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -6182,6 +6095,13 @@
       <c r="HP10" t="n">
         <v>2.531</v>
       </c>
+      <c r="HQ10" t="n">
+        <v>2.246</v>
+      </c>
+      <c r="HR10" t="n">
+        <v>2.332</v>
+      </c>
+      <c r="HS10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -6648,6 +6568,13 @@
       <c r="HP11" t="n">
         <v>752.622</v>
       </c>
+      <c r="HQ11" t="n">
+        <v>577.681</v>
+      </c>
+      <c r="HR11" t="n">
+        <v>140.57</v>
+      </c>
+      <c r="HS11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -7114,6 +7041,13 @@
       <c r="HP12" t="n">
         <v>12.599</v>
       </c>
+      <c r="HQ12" t="n">
+        <v>9.664999999999999</v>
+      </c>
+      <c r="HR12" t="n">
+        <v>2.339</v>
+      </c>
+      <c r="HS12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -7580,6 +7514,13 @@
       <c r="HP13" t="n">
         <v>32.776</v>
       </c>
+      <c r="HQ13" t="n">
+        <v>49.429</v>
+      </c>
+      <c r="HR13" t="n">
+        <v>43.434</v>
+      </c>
+      <c r="HS13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -8046,6 +7987,13 @@
       <c r="HP14" t="n">
         <v>0.549</v>
       </c>
+      <c r="HQ14" t="n">
+        <v>0.827</v>
+      </c>
+      <c r="HR14" t="n">
+        <v>0.723</v>
+      </c>
+      <c r="HS14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -8512,6 +8460,13 @@
       <c r="HP15" t="n">
         <v>4966.573</v>
       </c>
+      <c r="HQ15" t="n">
+        <v>5153.287</v>
+      </c>
+      <c r="HR15" t="n">
+        <v>5631.891</v>
+      </c>
+      <c r="HS15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -8978,6 +8933,13 @@
       <c r="HP16" t="n">
         <v>83.14100000000001</v>
       </c>
+      <c r="HQ16" t="n">
+        <v>86.214</v>
+      </c>
+      <c r="HR16" t="n">
+        <v>93.691</v>
+      </c>
+      <c r="HS16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -9660,6 +9622,13 @@
       <c r="HP17" t="n">
         <v>2650.601</v>
       </c>
+      <c r="HQ17" t="n">
+        <v>2691.953</v>
+      </c>
+      <c r="HR17" t="n">
+        <v>2993.229</v>
+      </c>
+      <c r="HS17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -10150,6 +10119,13 @@
       <c r="HP18" t="n">
         <v>44.371</v>
       </c>
+      <c r="HQ18" t="n">
+        <v>45.036</v>
+      </c>
+      <c r="HR18" t="n">
+        <v>49.795</v>
+      </c>
+      <c r="HS18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -10616,6 +10592,13 @@
       <c r="HP19" t="n">
         <v>1611.632</v>
       </c>
+      <c r="HQ19" t="n">
+        <v>1800.776</v>
+      </c>
+      <c r="HR19" t="n">
+        <v>1916.657</v>
+      </c>
+      <c r="HS19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -11082,6 +11065,13 @@
       <c r="HP20" t="n">
         <v>26.979</v>
       </c>
+      <c r="HQ20" t="n">
+        <v>30.127</v>
+      </c>
+      <c r="HR20" t="n">
+        <v>31.885</v>
+      </c>
+      <c r="HS20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -11548,6 +11538,13 @@
       <c r="HP21" t="n">
         <v>1038.969</v>
       </c>
+      <c r="HQ21" t="n">
+        <v>891.177</v>
+      </c>
+      <c r="HR21" t="n">
+        <v>1076.572</v>
+      </c>
+      <c r="HS21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -12014,6 +12011,13 @@
       <c r="HP22" t="n">
         <v>17.392</v>
       </c>
+      <c r="HQ22" t="n">
+        <v>14.909</v>
+      </c>
+      <c r="HR22" t="n">
+        <v>17.91</v>
+      </c>
+      <c r="HS22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -12480,6 +12484,13 @@
       <c r="HP23" t="n">
         <v>0</v>
       </c>
+      <c r="HQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -12892,6 +12903,9 @@
       <c r="HN24" t="inlineStr"/>
       <c r="HO24" t="inlineStr"/>
       <c r="HP24" t="inlineStr"/>
+      <c r="HQ24" t="inlineStr"/>
+      <c r="HR24" t="inlineStr"/>
+      <c r="HS24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -13574,6 +13588,13 @@
       <c r="HP25" t="n">
         <v>0</v>
       </c>
+      <c r="HQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -14064,6 +14085,13 @@
       <c r="HP26" t="n">
         <v>0</v>
       </c>
+      <c r="HQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -14746,6 +14774,13 @@
       <c r="HP27" t="n">
         <v>968.135</v>
       </c>
+      <c r="HQ27" t="n">
+        <v>878.389</v>
+      </c>
+      <c r="HR27" t="n">
+        <v>813.225</v>
+      </c>
+      <c r="HS27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -15236,6 +15271,13 @@
       <c r="HP28" t="n">
         <v>16.207</v>
       </c>
+      <c r="HQ28" t="n">
+        <v>14.695</v>
+      </c>
+      <c r="HR28" t="n">
+        <v>13.529</v>
+      </c>
+      <c r="HS28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -15702,6 +15744,13 @@
       <c r="HP29" t="n">
         <v>968.135</v>
       </c>
+      <c r="HQ29" t="n">
+        <v>878.389</v>
+      </c>
+      <c r="HR29" t="n">
+        <v>813.225</v>
+      </c>
+      <c r="HS29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -16168,6 +16217,13 @@
       <c r="HP30" t="n">
         <v>16.207</v>
       </c>
+      <c r="HQ30" t="n">
+        <v>14.695</v>
+      </c>
+      <c r="HR30" t="n">
+        <v>13.529</v>
+      </c>
+      <c r="HS30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -16634,6 +16690,13 @@
       <c r="HP31" t="n">
         <v>0</v>
       </c>
+      <c r="HQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -17100,6 +17163,13 @@
       <c r="HP32" t="n">
         <v>0</v>
       </c>
+      <c r="HQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR32" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -17566,6 +17636,13 @@
       <c r="HP33" t="n">
         <v>970.1900000000001</v>
       </c>
+      <c r="HQ33" t="n">
+        <v>1250.712</v>
+      </c>
+      <c r="HR33" t="n">
+        <v>1508.159</v>
+      </c>
+      <c r="HS33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -18032,6 +18109,13 @@
       <c r="HP34" t="n">
         <v>16.241</v>
       </c>
+      <c r="HQ34" t="n">
+        <v>20.924</v>
+      </c>
+      <c r="HR34" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="HS34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -18498,6 +18582,13 @@
       <c r="HP35" t="n">
         <v>0</v>
       </c>
+      <c r="HQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -18964,6 +19055,13 @@
       <c r="HP36" t="n">
         <v>0</v>
       </c>
+      <c r="HQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR36" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -19430,6 +19528,13 @@
       <c r="HP37" t="n">
         <v>970.1900000000001</v>
       </c>
+      <c r="HQ37" t="n">
+        <v>1250.712</v>
+      </c>
+      <c r="HR37" t="n">
+        <v>1508.159</v>
+      </c>
+      <c r="HS37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -19896,6 +20001,13 @@
       <c r="HP38" t="n">
         <v>16.241</v>
       </c>
+      <c r="HQ38" t="n">
+        <v>20.924</v>
+      </c>
+      <c r="HR38" t="n">
+        <v>25.09</v>
+      </c>
+      <c r="HS38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -20362,6 +20474,13 @@
       <c r="HP39" t="n">
         <v>0</v>
       </c>
+      <c r="HQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR39" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -20828,6 +20947,13 @@
       <c r="HP40" t="n">
         <v>0</v>
       </c>
+      <c r="HQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR40" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -21510,6 +21636,13 @@
       <c r="HP41" t="n">
         <v>0</v>
       </c>
+      <c r="HQ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR41" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -22000,6 +22133,13 @@
       <c r="HP42" t="n">
         <v>0</v>
       </c>
+      <c r="HQ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR42" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -22466,6 +22606,13 @@
       <c r="HP43" t="n">
         <v>0</v>
       </c>
+      <c r="HQ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR43" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -22932,6 +23079,13 @@
       <c r="HP44" t="n">
         <v>0</v>
       </c>
+      <c r="HQ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HR44" t="n">
+        <v>0</v>
+      </c>
+      <c r="HS44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -23230,6 +23384,13 @@
       <c r="HP45" t="n">
         <v>1007.125</v>
       </c>
+      <c r="HQ45" t="n">
+        <v>824.033</v>
+      </c>
+      <c r="HR45" t="n">
+        <v>379.217</v>
+      </c>
+      <c r="HS45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -23528,6 +23689,13 @@
       <c r="HP46" t="n">
         <v>16.859</v>
       </c>
+      <c r="HQ46" t="n">
+        <v>13.786</v>
+      </c>
+      <c r="HR46" t="n">
+        <v>6.309</v>
+      </c>
+      <c r="HS46" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
